--- a/datosSesionesSin0CorValues.xlsx
+++ b/datosSesionesSin0CorValues.xlsx
@@ -533,13 +533,13 @@
         <v>0.3204301075268817</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2759750180735694</v>
+        <v>0.2736598451108223</v>
       </c>
       <c r="E2" t="n">
         <v>0.2008090658902972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02050252797957693</v>
+        <v>0.3529891924480775</v>
       </c>
       <c r="G2" t="n">
         <v>0.4928485544872362</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1856021735934717</v>
+        <v>0.1864281177390625</v>
       </c>
       <c r="E3" t="n">
         <v>0.2362766411644276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07873986450838151</v>
+        <v>0.1963022990930435</v>
       </c>
       <c r="G3" t="n">
         <v>0.2946267115393076</v>
@@ -649,58 +649,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2759750180735694</v>
+        <v>0.2736598451108223</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1856021735934717</v>
+        <v>0.1864281177390625</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.08465304330548684</v>
+        <v>-0.08180767125136898</v>
       </c>
       <c r="F4" t="n">
-        <v>0.110470342451177</v>
+        <v>0.6951571067372446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5638743230246542</v>
+        <v>0.5601347393331584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4907348339550212</v>
+        <v>0.4861925826508254</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5690929169425345</v>
+        <v>0.569652880088814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6953326742411303</v>
+        <v>0.6881233188041727</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6110688286560689</v>
+        <v>0.6027468336236299</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4589154573663985</v>
+        <v>0.4625306791623252</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3883307157302615</v>
+        <v>0.3876953266355978</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2984371694854442</v>
+        <v>0.2981241672754521</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4405881728023314</v>
+        <v>0.4394737159458788</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8466550740545056</v>
+        <v>0.8417017335151822</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.729067324081597</v>
+        <v>0.7266246077541165</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2472793852901902</v>
+        <v>0.251126652553009</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2928010632613491</v>
+        <v>0.2968432958363747</v>
       </c>
     </row>
     <row r="5">
@@ -716,13 +716,13 @@
         <v>0.2362766411644276</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08465304330548684</v>
+        <v>-0.08180767125136898</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09571819465645168</v>
+        <v>-0.03786232265452397</v>
       </c>
       <c r="G5" t="n">
         <v>0.4364489611273388</v>
@@ -771,58 +771,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02050252797957693</v>
+        <v>0.3529891924480775</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07873986450838151</v>
+        <v>0.1963022990930435</v>
       </c>
       <c r="D6" t="n">
-        <v>0.110470342451177</v>
+        <v>0.6951571067372446</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09571819465645168</v>
+        <v>-0.03786232265452397</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01992131992332155</v>
+        <v>0.5842623947194407</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.02362006202903096</v>
+        <v>0.5163443037123203</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1579579932183655</v>
+        <v>0.5631950061247516</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.09965007806094646</v>
+        <v>0.6345502727642356</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1444622491055067</v>
+        <v>0.5851777675295414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1740464463228547</v>
+        <v>0.3027647995428249</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1064767157076286</v>
+        <v>0.4665345090075186</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0913386963666091</v>
+        <v>0.3670973548999331</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09945483476926659</v>
+        <v>0.5100991245485388</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002464692983196959</v>
+        <v>0.7545298775953806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0803103120838241</v>
+        <v>0.6880875359152705</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2404627810305536</v>
+        <v>0.3627172554426169</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2416352564103969</v>
+        <v>0.3670999124665891</v>
       </c>
     </row>
     <row r="7">
@@ -838,13 +838,13 @@
         <v>0.2946267115393076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5638743230246542</v>
+        <v>0.5601347393331584</v>
       </c>
       <c r="E7" t="n">
         <v>0.4364489611273388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01992131992332155</v>
+        <v>0.5842623947194407</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.3063378386141006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4907348339550212</v>
+        <v>0.4861925826508254</v>
       </c>
       <c r="E8" t="n">
         <v>0.4751477765981752</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02362006202903096</v>
+        <v>0.5163443037123203</v>
       </c>
       <c r="G8" t="n">
         <v>0.9746514755436448</v>
@@ -960,13 +960,13 @@
         <v>0.1293123820835779</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5690929169425345</v>
+        <v>0.569652880088814</v>
       </c>
       <c r="E9" t="n">
         <v>0.1196984871109917</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1579579932183655</v>
+        <v>0.5631950061247516</v>
       </c>
       <c r="G9" t="n">
         <v>0.6580043845777352</v>
@@ -1021,13 +1021,13 @@
         <v>0.2958165423011472</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6953326742411303</v>
+        <v>0.6881233188041727</v>
       </c>
       <c r="E10" t="n">
         <v>0.3244894656970541</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09965007806094646</v>
+        <v>0.6345502727642356</v>
       </c>
       <c r="G10" t="n">
         <v>0.8936595376126368</v>
@@ -1082,13 +1082,13 @@
         <v>0.293212835328597</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6110688286560689</v>
+        <v>0.6027468336236299</v>
       </c>
       <c r="E11" t="n">
         <v>0.3159144826226409</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1444622491055067</v>
+        <v>0.5851777675295414</v>
       </c>
       <c r="G11" t="n">
         <v>0.8842018132374618</v>
@@ -1143,13 +1143,13 @@
         <v>0.05509227580264558</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4589154573663985</v>
+        <v>0.4625306791623252</v>
       </c>
       <c r="E12" t="n">
         <v>0.08454054878926871</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1740464463228547</v>
+        <v>0.3027647995428249</v>
       </c>
       <c r="G12" t="n">
         <v>0.1731442626583288</v>
@@ -1204,13 +1204,13 @@
         <v>0.2533078842145831</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3883307157302615</v>
+        <v>0.3876953266355978</v>
       </c>
       <c r="E13" t="n">
         <v>0.4601619629539652</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1064767157076286</v>
+        <v>0.4665345090075186</v>
       </c>
       <c r="G13" t="n">
         <v>0.9421833942788589</v>
@@ -1265,13 +1265,13 @@
         <v>0.2673707972322834</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2984371694854442</v>
+        <v>0.2981241672754521</v>
       </c>
       <c r="E14" t="n">
         <v>0.5423004202311099</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0913386963666091</v>
+        <v>0.3670973548999331</v>
       </c>
       <c r="G14" t="n">
         <v>0.8954080395008817</v>
@@ -1326,13 +1326,13 @@
         <v>0.1241789534509339</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4405881728023314</v>
+        <v>0.4394737159458788</v>
       </c>
       <c r="E15" t="n">
         <v>0.09853360894158877</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09945483476926659</v>
+        <v>0.5100991245485388</v>
       </c>
       <c r="G15" t="n">
         <v>0.684331868976878</v>
@@ -1387,13 +1387,13 @@
         <v>0.2913622391103139</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8466550740545056</v>
+        <v>0.8417017335151822</v>
       </c>
       <c r="E16" t="n">
         <v>0.1891452410046342</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002464692983196959</v>
+        <v>0.7545298775953806</v>
       </c>
       <c r="G16" t="n">
         <v>0.7693087788509778</v>
@@ -1448,13 +1448,13 @@
         <v>0.2724628775823577</v>
       </c>
       <c r="D17" t="n">
-        <v>0.729067324081597</v>
+        <v>0.7266246077541165</v>
       </c>
       <c r="E17" t="n">
         <v>0.2623159544768415</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0803103120838241</v>
+        <v>0.6880875359152705</v>
       </c>
       <c r="G17" t="n">
         <v>0.7900050055294243</v>
@@ -1509,13 +1509,13 @@
         <v>0.1712378630355684</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2472793852901902</v>
+        <v>0.251126652553009</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2694653684619468</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2404627810305536</v>
+        <v>0.3627172554426169</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1069060944714225</v>
@@ -1570,13 +1570,13 @@
         <v>0.1886554443143671</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2928010632613491</v>
+        <v>0.2968432958363747</v>
       </c>
       <c r="E19" t="n">
         <v>-0.1855679343257708</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2416352564103969</v>
+        <v>0.3670999124665891</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0720738856825343</v>

--- a/datosSesionesSin0CorValues.xlsx
+++ b/datosSesionesSin0CorValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -580,6 +590,12 @@
       <c r="S2" t="n">
         <v>0.1915841187409808</v>
       </c>
+      <c r="T2" t="n">
+        <v>0.1029681131978639</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.1029681131978642</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -641,6 +657,12 @@
       <c r="S3" t="n">
         <v>0.1886554443143671</v>
       </c>
+      <c r="T3" t="n">
+        <v>0.09809792979217138</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.09809792979217195</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -702,6 +724,12 @@
       <c r="S4" t="n">
         <v>0.2968432958363747</v>
       </c>
+      <c r="T4" t="n">
+        <v>-0.1943137629181564</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1943137629181565</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -763,6 +791,12 @@
       <c r="S5" t="n">
         <v>-0.1855679343257708</v>
       </c>
+      <c r="T5" t="n">
+        <v>0.2681607814774951</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.2681607814774958</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -824,6 +858,12 @@
       <c r="S6" t="n">
         <v>0.3670999124665891</v>
       </c>
+      <c r="T6" t="n">
+        <v>-0.2119579282287624</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2119579282287626</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -885,6 +925,12 @@
       <c r="S7" t="n">
         <v>-0.0720738856825343</v>
       </c>
+      <c r="T7" t="n">
+        <v>0.06840748805652674</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.06840748805652726</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -946,6 +992,12 @@
       <c r="S8" t="n">
         <v>-0.1385720365652411</v>
       </c>
+      <c r="T8" t="n">
+        <v>0.2514627400245616</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.251462740024562</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1007,6 +1059,12 @@
       <c r="S9" t="n">
         <v>0.1825401636627063</v>
       </c>
+      <c r="T9" t="n">
+        <v>-0.576941640870986</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5769416408709855</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1068,6 +1126,12 @@
       <c r="S10" t="n">
         <v>0.04511219382812461</v>
       </c>
+      <c r="T10" t="n">
+        <v>0.1058433506187627</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.105843350618763</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1129,6 +1193,12 @@
       <c r="S11" t="n">
         <v>-0.07485953644535238</v>
       </c>
+      <c r="T11" t="n">
+        <v>0.2116809825691191</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.2116809825691194</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1190,6 +1260,12 @@
       <c r="S12" t="n">
         <v>0.5124737511887885</v>
       </c>
+      <c r="T12" t="n">
+        <v>-0.4303782807676835</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.4303782807676838</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1251,6 +1327,12 @@
       <c r="S13" t="n">
         <v>-0.1496913939456564</v>
       </c>
+      <c r="T13" t="n">
+        <v>0.03106525857928259</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.03106525857928323</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1312,6 +1394,12 @@
       <c r="S14" t="n">
         <v>-0.1740267550129788</v>
       </c>
+      <c r="T14" t="n">
+        <v>0.2461271110781625</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.246127111078163</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1373,6 +1461,12 @@
       <c r="S15" t="n">
         <v>-0.03740625569589318</v>
       </c>
+      <c r="T15" t="n">
+        <v>-0.4637246534673207</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.46372465346732</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1434,6 +1528,12 @@
       <c r="S16" t="n">
         <v>0.176980936365563</v>
       </c>
+      <c r="T16" t="n">
+        <v>0.02870599836912888</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.02870599836912884</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1495,6 +1595,12 @@
       <c r="S17" t="n">
         <v>0.004344837280167695</v>
       </c>
+      <c r="T17" t="n">
+        <v>0.08198043930846757</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.08198043930846766</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1556,6 +1662,12 @@
       <c r="S18" t="n">
         <v>0.9455254530427819</v>
       </c>
+      <c r="T18" t="n">
+        <v>-0.2372653173531443</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2372653173531457</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1615,6 +1727,146 @@
         <v>0.9455254530427819</v>
       </c>
       <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.3512018489691448</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.351201848969146</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1029681131978639</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.09809792979217138</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.1943137629181564</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2681607814774951</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2119579282287624</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.06840748805652674</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2514627400245616</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.576941640870986</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1058433506187627</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2116809825691191</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.4303782807676835</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.03106525857928259</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2461271110781625</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.4637246534673207</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.02870599836912888</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.08198043930846757</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.2372653173531443</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.3512018489691448</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.1029681131978642</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.09809792979217195</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1943137629181565</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2681607814774958</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2119579282287626</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.06840748805652726</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.251462740024562</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5769416408709855</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.105843350618763</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.2116809825691194</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4303782807676838</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.03106525857928323</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.246127111078163</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.46372465346732</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.02870599836912884</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.08198043930846766</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2372653173531457</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.351201848969146</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
     </row>
